--- a/pipeline_output/JK_2W_H&M.xlsx
+++ b/pipeline_output/JK_2W_H&M.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9316,12 +9316,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11141,12 +11141,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11883,12 +11883,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -12244,12 +12244,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -12498,12 +12498,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -12869,12 +12869,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -13220,12 +13220,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -13591,12 +13591,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -13845,12 +13845,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -14216,12 +14216,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -14831,12 +14831,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15075,12 +15075,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15202,12 +15202,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15329,12 +15329,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15583,12 +15583,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15700,12 +15700,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15817,12 +15817,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15934,12 +15934,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16051,12 +16051,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16168,12 +16168,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16676,12 +16676,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16793,12 +16793,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16920,12 +16920,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17047,12 +17047,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17164,12 +17164,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17291,12 +17291,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17418,12 +17418,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17789,12 +17789,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17906,12 +17906,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -18033,12 +18033,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18160,12 +18160,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18287,12 +18287,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18531,12 +18531,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18765,12 +18765,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18882,12 +18882,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19126,12 +19126,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19253,12 +19253,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19380,12 +19380,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19507,12 +19507,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19624,12 +19624,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19751,12 +19751,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19878,12 +19878,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19995,12 +19995,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20249,12 +20249,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20366,12 +20366,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20493,12 +20493,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20620,12 +20620,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -20747,12 +20747,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -20874,12 +20874,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -21001,12 +21001,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21063,7 +21063,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -21128,12 +21128,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -21255,12 +21255,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -21382,12 +21382,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -21509,12 +21509,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -21753,12 +21753,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -21870,12 +21870,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -21987,12 +21987,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -22104,12 +22104,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -22338,12 +22338,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -22455,12 +22455,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -22572,12 +22572,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -22689,12 +22689,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22751,7 +22751,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -22806,12 +22806,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22868,7 +22868,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -22923,12 +22923,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -23040,12 +23040,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -23157,12 +23157,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23391,12 +23391,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>JAMMU AND KASHMIR</t>
+          <t>JAMMU AND KASHMIR, LADAKH</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -23508,12 +23508,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
